--- a/src/assets/files/sample_upload_tasks_against_milestone.xlsx
+++ b/src/assets/files/sample_upload_tasks_against_milestone.xlsx
@@ -5,43 +5,25 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rehab.zafar\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rehab.zafar\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB7B0720-D0C2-4751-AB49-93B72119BAB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C3B448E-022A-4B9D-8285-82468DE0E49C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-60" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$I$4</definedName>
+  </definedNames>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="22">
-  <si>
-    <t>name</t>
-  </si>
-  <si>
-    <t>priority</t>
-  </si>
-  <si>
-    <t>assigned_to</t>
-  </si>
-  <si>
-    <t>tags</t>
-  </si>
-  <si>
-    <t>description</t>
-  </si>
-  <si>
-    <t>2024-11-10</t>
-  </si>
-  <si>
-    <t>2024-11-15</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="34">
   <si>
     <t>high</t>
   </si>
@@ -49,12 +31,6 @@
     <t>This is the first task.</t>
   </si>
   <si>
-    <t>started_at</t>
-  </si>
-  <si>
-    <t>ended_at</t>
-  </si>
-  <si>
     <t>rehab.zafar@srl.com.pk</t>
   </si>
   <si>
@@ -86,13 +62,76 @@
   </si>
   <si>
     <t>Task 3</t>
+  </si>
+  <si>
+    <t>task_teams</t>
+  </si>
+  <si>
+    <t>cloud team, D365</t>
+  </si>
+  <si>
+    <t>cloud team, D365, D656</t>
+  </si>
+  <si>
+    <t>cloud team</t>
+  </si>
+  <si>
+    <t>task_tags</t>
+  </si>
+  <si>
+    <t>task_name</t>
+  </si>
+  <si>
+    <t>task_started_at</t>
+  </si>
+  <si>
+    <t>task_ended_at</t>
+  </si>
+  <si>
+    <t>task_priority</t>
+  </si>
+  <si>
+    <t>task_assigned_to</t>
+  </si>
+  <si>
+    <t>task_description</t>
+  </si>
+  <si>
+    <t>task_status</t>
+  </si>
+  <si>
+    <t>in_progress</t>
+  </si>
+  <si>
+    <t>completed</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>Task 4</t>
+  </si>
+  <si>
+    <t>Task 5</t>
+  </si>
+  <si>
+    <t>cancelled</t>
+  </si>
+  <si>
+    <t>on_hold</t>
+  </si>
+  <si>
+    <t>This is the fourth task.</t>
+  </si>
+  <si>
+    <t>This is the fifth task.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -116,13 +155,37 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -149,18 +212,31 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="22" fontId="3" fillId="2" borderId="0" xfId="2" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="3"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="4">
+    <cellStyle name="Bad" xfId="3" builtinId="27"/>
+    <cellStyle name="Good" xfId="2" builtinId="26"/>
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
@@ -498,113 +574,202 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="42.21875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="27.77734375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="30.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.44140625" customWidth="1"/>
+    <col min="5" max="5" width="16.21875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21.77734375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.21875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="21.21875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="3">
+        <v>45597</v>
+      </c>
+      <c r="C2" s="3">
+        <v>45597</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E2" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="F2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="3">
+        <v>45597</v>
+      </c>
+      <c r="C3" s="3">
+        <v>45597</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="3">
+        <v>45597</v>
+      </c>
+      <c r="C4" s="3">
+        <v>45597</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G4" t="s">
         <v>9</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="1" t="s">
+      <c r="H4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" s="3">
+        <v>45597</v>
+      </c>
+      <c r="C5" s="3">
+        <v>45597</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>4</v>
+      <c r="G5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I5" t="s">
+        <v>32</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" t="s">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B6" s="3">
+        <v>45597</v>
+      </c>
+      <c r="C6" s="3">
+        <v>45597</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E6" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D3" t="s">
+      <c r="F6" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G6" t="s">
+        <v>9</v>
+      </c>
+      <c r="H6" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D4" t="s">
-        <v>16</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4" t="s">
-        <v>18</v>
-      </c>
-      <c r="G4" t="s">
-        <v>20</v>
+      <c r="I6" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:I4" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <hyperlinks>
-    <hyperlink ref="E2" r:id="rId1" xr:uid="{E7227BC0-F69E-4E2F-8810-E75C49BAEEE1}"/>
-    <hyperlink ref="E3" r:id="rId2" xr:uid="{A41DEF2F-C9B9-41C1-8AAD-EADFC568A863}"/>
-    <hyperlink ref="E4" r:id="rId3" xr:uid="{6F2BAC0B-4037-43CE-A170-750E022F503C}"/>
+    <hyperlink ref="F2" r:id="rId1" xr:uid="{E7227BC0-F69E-4E2F-8810-E75C49BAEEE1}"/>
+    <hyperlink ref="F3" r:id="rId2" xr:uid="{A41DEF2F-C9B9-41C1-8AAD-EADFC568A863}"/>
+    <hyperlink ref="F4" r:id="rId3" xr:uid="{6F2BAC0B-4037-43CE-A170-750E022F503C}"/>
+    <hyperlink ref="F5" r:id="rId4" xr:uid="{AE680BF5-98D3-4322-81DF-D0AD11829DD0}"/>
+    <hyperlink ref="F6" r:id="rId5" xr:uid="{B494BC20-BB55-4451-977A-72BBB2DD3647}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
